--- a/Config/GuideStepConfig.xlsx
+++ b/Config/GuideStepConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,14 +617,11 @@
           <t>Wait</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>DealFinished</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>false</t>
@@ -656,22 +653,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Board.PlayerHand</t>
+          <t>GameUI.PeekGood</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>点选 3 张牌组成牌型</t>
+          <t>长按搓牌技能，可查看技能详情</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SelectCards</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>PeekGoodTipShown</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -685,7 +677,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -700,33 +692,31 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>GameUI.CompareBtn</t>
+          <t>Wait</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>点开牌与敌人比大小</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>点击任意地方关闭</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PeekGoodTipClosed</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -741,33 +731,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wait</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>GamePhase</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>RoundSettle</t>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GameUI.PeekGood</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>点击搓牌技能</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -782,32 +770,206 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Board.PlayerCard.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>点选手牌里的「3」，搓成 A</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RubCard</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Board.PlayerHand</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>点选三张 A 组成豹子</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SelectHandType</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ThreeOfAKind</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Click</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GameUI.CompareBtn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>点开牌与敌人比大小</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GamePhase</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RoundSettle</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>GameUI.NextRoundBtn</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>点下一局继续</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
         <v>16</v>
       </c>
     </row>

--- a/Config/GuideStepConfig.xlsx
+++ b/Config/GuideStepConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +973,186 @@
         <v>16</v>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Navigation.TalentBtn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>点击天赋</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TalentPopupOpen</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TalentPopup.BuyBtn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>点击抽取天赋</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TalentDrawn</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>这是抽到的天赋，点下一步继续</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/GuideStepConfig.xlsx
+++ b/Config/GuideStepConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -653,17 +653,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GameUI.PeekGood</t>
+          <t>Board.PlayerHand</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>长按搓牌技能，可查看技能详情</t>
+          <t>请选3张进行亮牌，选择后点击开战</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PeekGoodTipShown</t>
+          <t>SelectGuideCards</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0,1,2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -677,7 +682,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -692,31 +697,31 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wait</t>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GameUI.CompareBtn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>点击任意地方关闭</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PeekGoodTipClosed</t>
+          <t>请选3张进行亮牌，选择后点击开战</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -731,31 +736,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GameUI.PeekGood</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>点击搓牌技能</t>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>GamePhase</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RoundSettle,Shop</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -763,11 +768,11 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Wait</t>
@@ -775,22 +780,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Board.PlayerCard.2</t>
+          <t>GameUI.SkillButtons</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>点选手牌里的「3」，搓成 A</t>
+          <t>长按查看技能详情</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>RubCard</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>PeekGoodTipShown</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -812,59 +812,49 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Wait</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Board.PlayerHand</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>点选三张 A 组成豹子</t>
+          <t>点击任意地方关闭</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>SelectHandType</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ThreeOfAKind</t>
+          <t>PeekGoodTipClosed</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -873,12 +863,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GameUI.CompareBtn</t>
+          <t>GameUI.YiwuBtn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>点开牌与敌人比大小</t>
+          <t>点击此处可以查看当前各个圣物具体效果!</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -897,13 +887,13 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -912,12 +902,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>GamePhase</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>RoundSettle</t>
+          <t>RemainListClosed</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -936,13 +921,13 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -951,12 +936,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GameUI.NextRoundBtn</t>
+          <t>GameUI.PeekGood</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>点下一局继续</t>
+          <t>点击搓牌，选择一张进行搓牌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -975,27 +960,37 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Click</t>
+          <t>Wait</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Navigation.TalentBtn</t>
+          <t>Board.PlayerCard.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>点击天赋</t>
+          <t>点击搓牌，选择一张进行搓牌</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>RubCard</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1009,52 +1004,67 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Wait</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Board.PlayerHand</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>请选3张进行亮牌，选择后点击开战</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TalentPopupOpen</t>
+          <t>SelectGuideCards</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0,1,2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1063,12 +1073,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TalentPopup.BuyBtn</t>
+          <t>GameUI.CompareBtn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>点击抽取天赋</t>
+          <t>请选3张进行亮牌，选择后点击开战</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1093,30 +1103,35 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wait</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>TalentDrawn</t>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Navigation.TalentBtn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>点击天赋</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1127,21 +1142,21 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dialog</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>这是抽到的天赋，点下一步继续</t>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TalentPopupOpen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1151,6 +1166,230 @@
       </c>
       <c r="L17" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TalentPopup.BuyBtn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>点击抽取天赋</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TalentDrawn</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dialog</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>这是抽到的天赋，点下一步继续</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Shop.SellOffers</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>点击消耗金币购买圣物</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ShopOfferClicked</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Wait</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ShopBought</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GameUI.Bonds</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>部分圣物可以凑成羁绊,羁绊可以在这里查看效果!</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
